--- a/Cheburashka_electronix/Расчет.xlsx
+++ b/Cheburashka_electronix/Расчет.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\reposGitHub\Cheburashka\Cheburashka_electronix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2191F7A7-8706-4A3B-AE5D-FCE540BD73CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D1DE29-75AA-4987-9724-14B682366A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2F3FF230-4415-46E5-A273-3AAB75EDC142}"/>
   </bookViews>
@@ -211,31 +211,31 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -553,39 +553,39 @@
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="11"/>
-    <col min="2" max="3" width="10.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="11"/>
+    <col min="1" max="1" width="8.88671875" style="7"/>
+    <col min="2" max="3" width="10.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="50.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="9"/>
+      <c r="F1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="9"/>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="4"/>
+      <c r="J1" s="9"/>
     </row>
     <row r="2" spans="1:10" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6"/>
+      <c r="A2" s="4"/>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
@@ -613,13 +613,13 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="10">
         <v>5</v>
       </c>
-      <c r="C3" s="9"/>
+      <c r="C3" s="11"/>
       <c r="D3" s="1">
         <v>0.1</v>
       </c>
@@ -647,13 +647,13 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="10">
         <v>5</v>
       </c>
-      <c r="C4" s="9"/>
+      <c r="C4" s="11"/>
       <c r="D4" s="1">
         <v>2</v>
       </c>
@@ -681,7 +681,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="51" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="1">
@@ -717,7 +717,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="1">
@@ -753,7 +753,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="1">
@@ -789,7 +789,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -799,27 +799,27 @@
         <v>14</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" ref="B8:I8" si="4">SUM(D3:D7)</f>
+        <f>SUM(D3:D7)</f>
         <v>9.1999999999999993</v>
       </c>
       <c r="E8" s="1">
-        <f t="shared" si="4"/>
+        <f>SUM(E3:E7)</f>
         <v>17.799999999999997</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" si="4"/>
+        <f>SUM(F3:F7)</f>
         <v>45.8</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" si="4"/>
+        <f>SUM(G3:G7)</f>
         <v>160.51999999999998</v>
       </c>
       <c r="H8" s="1">
-        <f t="shared" si="4"/>
+        <f>SUM(H3:H7)</f>
         <v>11</v>
       </c>
       <c r="I8" s="1">
-        <f t="shared" si="4"/>
+        <f>SUM(I3:I7)</f>
         <v>84.8</v>
       </c>
       <c r="J8" s="1">
@@ -828,18 +828,18 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="7" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
